--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/38.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/38.xlsx
@@ -426,13 +426,13 @@
         <v>-14.79374935998288</v>
       </c>
       <c r="E2">
-        <v>-28.31606097147752</v>
+        <v>-30.51582156239149</v>
       </c>
       <c r="F2">
-        <v>-3.613257365222737</v>
+        <v>-3.701549761861445</v>
       </c>
       <c r="G2">
-        <v>-19.77387972509852</v>
+        <v>-24.55236253830179</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.44938039399149</v>
       </c>
       <c r="E3">
-        <v>-29.73012226511267</v>
+        <v>-30.09088088269672</v>
       </c>
       <c r="F3">
-        <v>-3.070728021623604</v>
+        <v>-4.072049050395968</v>
       </c>
       <c r="G3">
-        <v>-20.25791624366813</v>
+        <v>-24.79039738366647</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.04715129130677</v>
       </c>
       <c r="E4">
-        <v>-30.10090239567569</v>
+        <v>-31.41104653201982</v>
       </c>
       <c r="F4">
-        <v>-3.310594535870147</v>
+        <v>-3.913946105151733</v>
       </c>
       <c r="G4">
-        <v>-19.37801131060355</v>
+        <v>-23.86152286098499</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.61452990711804</v>
       </c>
       <c r="E5">
-        <v>-29.29079688773253</v>
+        <v>-31.1548662289319</v>
       </c>
       <c r="F5">
-        <v>-3.29450487562224</v>
+        <v>-3.92689290101045</v>
       </c>
       <c r="G5">
-        <v>-19.31097772925161</v>
+        <v>-23.4102806065274</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.14092256790103</v>
       </c>
       <c r="E6">
-        <v>-29.69264234998818</v>
+        <v>-33.12564000317401</v>
       </c>
       <c r="F6">
-        <v>-3.048405686745485</v>
+        <v>-3.556566236420709</v>
       </c>
       <c r="G6">
-        <v>-18.98637873912607</v>
+        <v>-25.52571755084892</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.63392104488723</v>
       </c>
       <c r="E7">
-        <v>-30.68406116448745</v>
+        <v>-33.2504968242765</v>
       </c>
       <c r="F7">
-        <v>-3.151072590125678</v>
+        <v>-3.479476183574863</v>
       </c>
       <c r="G7">
-        <v>-19.23622561097487</v>
+        <v>-23.58242566402396</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.09709459424621</v>
       </c>
       <c r="E8">
-        <v>-30.64159992795453</v>
+        <v>-33.46811717118911</v>
       </c>
       <c r="F8">
-        <v>-3.259858141310171</v>
+        <v>-3.227958344908432</v>
       </c>
       <c r="G8">
-        <v>-19.34402193955185</v>
+        <v>-23.13950943159764</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.51960742563951</v>
       </c>
       <c r="E9">
-        <v>-31.11112343425481</v>
+        <v>-34.02388546496547</v>
       </c>
       <c r="F9">
-        <v>-3.140716737144619</v>
+        <v>-2.829279385167536</v>
       </c>
       <c r="G9">
-        <v>-18.3571267957491</v>
+        <v>-23.11044118649007</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.89333615433266</v>
       </c>
       <c r="E10">
-        <v>-31.6888095422283</v>
+        <v>-34.58082889774682</v>
       </c>
       <c r="F10">
-        <v>-3.243292577434675</v>
+        <v>-3.242693144745681</v>
       </c>
       <c r="G10">
-        <v>-17.77475383248098</v>
+        <v>-24.00786221600293</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.22537754189175</v>
       </c>
       <c r="E11">
-        <v>-32.58522097204665</v>
+        <v>-36.38436612688567</v>
       </c>
       <c r="F11">
-        <v>-2.830828249552836</v>
+        <v>-3.128770843424459</v>
       </c>
       <c r="G11">
-        <v>-17.55846099494547</v>
+        <v>-23.51275854369554</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.511329237109136</v>
       </c>
       <c r="E12">
-        <v>-32.79847587001586</v>
+        <v>-35.23753008444314</v>
       </c>
       <c r="F12">
-        <v>-2.809025370214981</v>
+        <v>-2.677685471235757</v>
       </c>
       <c r="G12">
-        <v>-18.18327846257258</v>
+        <v>-23.64419878851399</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.751743904202513</v>
       </c>
       <c r="E13">
-        <v>-33.17255046541947</v>
+        <v>-36.88841924749443</v>
       </c>
       <c r="F13">
-        <v>-2.897740616333111</v>
+        <v>-2.376463022413259</v>
       </c>
       <c r="G13">
-        <v>-17.11148934423354</v>
+        <v>-23.20814697226335</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.971707263417311</v>
       </c>
       <c r="E14">
-        <v>-33.08931258468449</v>
+        <v>-35.50772827882181</v>
       </c>
       <c r="F14">
-        <v>-2.628128937582784</v>
+        <v>-3.309759130999752</v>
       </c>
       <c r="G14">
-        <v>-17.02933981194929</v>
+        <v>-21.94873103021333</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.182603845089117</v>
       </c>
       <c r="E15">
-        <v>-34.31914197026558</v>
+        <v>-39.18404084043977</v>
       </c>
       <c r="F15">
-        <v>-2.548108236940417</v>
+        <v>-2.360480262314644</v>
       </c>
       <c r="G15">
-        <v>-16.79032007928668</v>
+        <v>-20.99815091570363</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.391597272009591</v>
       </c>
       <c r="E16">
-        <v>-35.43298355108821</v>
+        <v>-37.42076627370312</v>
       </c>
       <c r="F16">
-        <v>-2.62681050240818</v>
+        <v>-1.676675640675776</v>
       </c>
       <c r="G16">
-        <v>-16.49326813859342</v>
+        <v>-22.68059498785279</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.620008567570664</v>
       </c>
       <c r="E17">
-        <v>-35.77954313842121</v>
+        <v>-38.44191225582575</v>
       </c>
       <c r="F17">
-        <v>-2.594460933526456</v>
+        <v>-2.205395860545236</v>
       </c>
       <c r="G17">
-        <v>-15.5801501574061</v>
+        <v>-20.88524807063232</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.875827834865492</v>
       </c>
       <c r="E18">
-        <v>-36.93552669835923</v>
+        <v>-38.22011439164107</v>
       </c>
       <c r="F18">
-        <v>-2.271303365922164</v>
+        <v>-2.174655336873598</v>
       </c>
       <c r="G18">
-        <v>-15.008253415497</v>
+        <v>-21.09617616912145</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.159376637556531</v>
       </c>
       <c r="E19">
-        <v>-37.16515202986616</v>
+        <v>-39.46208914451073</v>
       </c>
       <c r="F19">
-        <v>-2.339601475378448</v>
+        <v>-1.876182201520303</v>
       </c>
       <c r="G19">
-        <v>-15.54535632378836</v>
+        <v>-22.60402206952944</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.482224108570146</v>
       </c>
       <c r="E20">
-        <v>-37.33706648861936</v>
+        <v>-40.51212679080229</v>
       </c>
       <c r="F20">
-        <v>-2.160195310012679</v>
+        <v>-1.151789572827596</v>
       </c>
       <c r="G20">
-        <v>-15.53401108422528</v>
+        <v>-21.80867012481062</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.850359793657231</v>
       </c>
       <c r="E21">
-        <v>-37.75885761464178</v>
+        <v>-42.32423415700065</v>
       </c>
       <c r="F21">
-        <v>-1.706465148945192</v>
+        <v>-1.235336394690688</v>
       </c>
       <c r="G21">
-        <v>-15.93106632929608</v>
+        <v>-20.17814699362662</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.263626455720086</v>
       </c>
       <c r="E22">
-        <v>-38.83093534392868</v>
+        <v>-41.73900361133038</v>
       </c>
       <c r="F22">
-        <v>-1.956478466991956</v>
+        <v>-1.297562575667177</v>
       </c>
       <c r="G22">
-        <v>-15.01848300121335</v>
+        <v>-20.99924505100435</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.729051969646988</v>
       </c>
       <c r="E23">
-        <v>-38.70309878692915</v>
+        <v>-41.47987980013747</v>
       </c>
       <c r="F23">
-        <v>-1.623541515359825</v>
+        <v>-0.726307974173803</v>
       </c>
       <c r="G23">
-        <v>-14.7049511648256</v>
+        <v>-20.51508107643148</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.251315220249917</v>
       </c>
       <c r="E24">
-        <v>-39.68283866696264</v>
+        <v>-40.79428694927221</v>
       </c>
       <c r="F24">
-        <v>-1.685331385356611</v>
+        <v>-1.704196490221325</v>
       </c>
       <c r="G24">
-        <v>-15.06388051219338</v>
+        <v>-20.17638247285419</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.8269491813976316</v>
       </c>
       <c r="E25">
-        <v>-38.94895869775359</v>
+        <v>-43.22921798811551</v>
       </c>
       <c r="F25">
-        <v>-1.657041646589116</v>
+        <v>-1.331483180817017</v>
       </c>
       <c r="G25">
-        <v>-14.59335101942399</v>
+        <v>-21.16217520499236</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.4533978899621842</v>
       </c>
       <c r="E26">
-        <v>-39.9088185768934</v>
+        <v>-43.53729007485733</v>
       </c>
       <c r="F26">
-        <v>-1.469540368436578</v>
+        <v>-1.934265407822003</v>
       </c>
       <c r="G26">
-        <v>-14.44944326010465</v>
+        <v>-19.33496097641086</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.1290575858531962</v>
       </c>
       <c r="E27">
-        <v>-39.31457410371087</v>
+        <v>-42.86359578944722</v>
       </c>
       <c r="F27">
-        <v>-1.635740802026455</v>
+        <v>-1.219343340503623</v>
       </c>
       <c r="G27">
-        <v>-15.17877133986102</v>
+        <v>-19.00333866392376</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.1529917656682119</v>
       </c>
       <c r="E28">
-        <v>-39.24581601861541</v>
+        <v>-41.85983461904004</v>
       </c>
       <c r="F28">
-        <v>-1.526782626897179</v>
+        <v>-1.567288281243416</v>
       </c>
       <c r="G28">
-        <v>-14.67041555375992</v>
+        <v>-20.6038119732478</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.399759477449284</v>
       </c>
       <c r="E29">
-        <v>-39.50119251756696</v>
+        <v>-42.83210251696088</v>
       </c>
       <c r="F29">
-        <v>-1.37861268515458</v>
+        <v>-1.739055441126063</v>
       </c>
       <c r="G29">
-        <v>-14.65657747340576</v>
+        <v>-19.61712870435957</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.6135449628063835</v>
       </c>
       <c r="E30">
-        <v>-38.76711329550157</v>
+        <v>-42.43098161054646</v>
       </c>
       <c r="F30">
-        <v>-1.610321530230694</v>
+        <v>-1.249980923290757</v>
       </c>
       <c r="G30">
-        <v>-14.20628203497241</v>
+        <v>-17.45479457192873</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.7984171655546698</v>
       </c>
       <c r="E31">
-        <v>-39.29693796168799</v>
+        <v>-43.24991990704158</v>
       </c>
       <c r="F31">
-        <v>-1.710557445030688</v>
+        <v>-1.428320462722478</v>
       </c>
       <c r="G31">
-        <v>-14.75452492900341</v>
+        <v>-20.26830473557036</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.957724978127807</v>
       </c>
       <c r="E32">
-        <v>-38.78317805704378</v>
+        <v>-40.1243060125484</v>
       </c>
       <c r="F32">
-        <v>-1.685562606420265</v>
+        <v>-1.171642118330587</v>
       </c>
       <c r="G32">
-        <v>-13.99799078600531</v>
+        <v>-18.09154159040661</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.088611271282406</v>
       </c>
       <c r="E33">
-        <v>-38.18904679571144</v>
+        <v>-41.39384785093976</v>
       </c>
       <c r="F33">
-        <v>-1.391019437296132</v>
+        <v>-2.386654169979112</v>
       </c>
       <c r="G33">
-        <v>-14.98506966508549</v>
+        <v>-20.06428905616723</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.188419218451845</v>
       </c>
       <c r="E34">
-        <v>-38.11212840045416</v>
+        <v>-42.11210458482234</v>
       </c>
       <c r="F34">
-        <v>-1.641413636615559</v>
+        <v>-1.852889846768977</v>
       </c>
       <c r="G34">
-        <v>-14.57815727067151</v>
+        <v>-18.18834028670213</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.253965884591599</v>
       </c>
       <c r="E35">
-        <v>-37.38370977089836</v>
+        <v>-42.05283818124695</v>
       </c>
       <c r="F35">
-        <v>-1.371427411416231</v>
+        <v>-2.193694649389012</v>
       </c>
       <c r="G35">
-        <v>-15.26282940164865</v>
+        <v>-17.39265397688384</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.280201145738382</v>
       </c>
       <c r="E36">
-        <v>-37.98395447214106</v>
+        <v>-42.83021867177369</v>
       </c>
       <c r="F36">
-        <v>-1.593426555524786</v>
+        <v>-1.760238299598023</v>
       </c>
       <c r="G36">
-        <v>-14.95494204540535</v>
+        <v>-19.58438906424894</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.264918806496232</v>
       </c>
       <c r="E37">
-        <v>-37.72215886128362</v>
+        <v>-43.63656554629048</v>
       </c>
       <c r="F37">
-        <v>-1.595879715987802</v>
+        <v>-2.779807579781039</v>
       </c>
       <c r="G37">
-        <v>-14.88051601586423</v>
+        <v>-19.89185432593598</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.206953852446422</v>
       </c>
       <c r="E38">
-        <v>-36.90170352599593</v>
+        <v>-42.76949409956784</v>
       </c>
       <c r="F38">
-        <v>-1.736653751105299</v>
+        <v>-2.041723813449358</v>
       </c>
       <c r="G38">
-        <v>-15.19585541011642</v>
+        <v>-19.8029363832967</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.106559957186153</v>
       </c>
       <c r="E39">
-        <v>-36.99760981276738</v>
+        <v>-40.36408418278054</v>
       </c>
       <c r="F39">
-        <v>-1.745803612031751</v>
+        <v>-2.04952594064177</v>
       </c>
       <c r="G39">
-        <v>-15.23496288457183</v>
+        <v>-19.70646046519126</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.9666708113986745</v>
       </c>
       <c r="E40">
-        <v>-35.96186403044403</v>
+        <v>-41.91433253948536</v>
       </c>
       <c r="F40">
-        <v>-1.459837794145638</v>
+        <v>-1.259413475723114</v>
       </c>
       <c r="G40">
-        <v>-15.32142440242098</v>
+        <v>-20.644587962655</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.7903943845019864</v>
       </c>
       <c r="E41">
-        <v>-35.74729134653858</v>
+        <v>-39.37858408380929</v>
       </c>
       <c r="F41">
-        <v>-1.571447884830318</v>
+        <v>-2.480438066879605</v>
       </c>
       <c r="G41">
-        <v>-15.6252546851059</v>
+        <v>-20.82210106974349</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.5810712967087193</v>
       </c>
       <c r="E42">
-        <v>-35.02802476295228</v>
+        <v>-37.50370980362761</v>
       </c>
       <c r="F42">
-        <v>-1.761426079034603</v>
+        <v>-2.473003359459574</v>
       </c>
       <c r="G42">
-        <v>-15.03505890272848</v>
+        <v>-20.73679989810586</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.3436736192113495</v>
       </c>
       <c r="E43">
-        <v>-34.76487060989255</v>
+        <v>-38.33353908011119</v>
       </c>
       <c r="F43">
-        <v>-1.521478795786372</v>
+        <v>-1.346555310014254</v>
       </c>
       <c r="G43">
-        <v>-15.66763463382688</v>
+        <v>-18.0635823780547</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.08270499308891273</v>
       </c>
       <c r="E44">
-        <v>-34.09847848881981</v>
+        <v>-37.68687978452687</v>
       </c>
       <c r="F44">
-        <v>-1.522362503687188</v>
+        <v>-1.022390505447742</v>
       </c>
       <c r="G44">
-        <v>-15.7642860108459</v>
+        <v>-20.01006397550674</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.1987597457344329</v>
       </c>
       <c r="E45">
-        <v>-32.79663730956874</v>
+        <v>-37.66350606593628</v>
       </c>
       <c r="F45">
-        <v>-1.540785754601495</v>
+        <v>-1.868611295391545</v>
       </c>
       <c r="G45">
-        <v>-15.70630346099834</v>
+        <v>-20.60724666424479</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.4958074357511146</v>
       </c>
       <c r="E46">
-        <v>-33.79734855273175</v>
+        <v>-37.70711979910416</v>
       </c>
       <c r="F46">
-        <v>-1.331378656226598</v>
+        <v>-2.290088493638149</v>
       </c>
       <c r="G46">
-        <v>-15.31544886772259</v>
+        <v>-19.6348003964482</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.8032273301360722</v>
       </c>
       <c r="E47">
-        <v>-32.65229446481126</v>
+        <v>-39.27806328202403</v>
       </c>
       <c r="F47">
-        <v>-1.700895255240592</v>
+        <v>-1.550587310512149</v>
       </c>
       <c r="G47">
-        <v>-15.58132705634531</v>
+        <v>-20.90738237810789</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.119285022457811</v>
       </c>
       <c r="E48">
-        <v>-33.69859385580948</v>
+        <v>-36.39310155324646</v>
       </c>
       <c r="F48">
-        <v>-1.636618175103609</v>
+        <v>-1.831427464202942</v>
       </c>
       <c r="G48">
-        <v>-15.86722576911677</v>
+        <v>-21.29934269359375</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.439984258515418</v>
       </c>
       <c r="E49">
-        <v>-32.15877683898133</v>
+        <v>-38.38520896853871</v>
       </c>
       <c r="F49">
-        <v>-1.365540776528543</v>
+        <v>-1.943344001982259</v>
       </c>
       <c r="G49">
-        <v>-15.33305434890044</v>
+        <v>-19.28296720344384</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.759592757424636</v>
       </c>
       <c r="E50">
-        <v>-31.94785410512607</v>
+        <v>-35.86929070054222</v>
       </c>
       <c r="F50">
-        <v>-1.614340183991122</v>
+        <v>-1.921826981562141</v>
       </c>
       <c r="G50">
-        <v>-16.13223328426266</v>
+        <v>-19.77847145176149</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.077450044567401</v>
       </c>
       <c r="E51">
-        <v>-32.14510311171517</v>
+        <v>-34.87133956228689</v>
       </c>
       <c r="F51">
-        <v>-1.44439428591123</v>
+        <v>-1.614884978826033</v>
       </c>
       <c r="G51">
-        <v>-15.91295267937796</v>
+        <v>-20.83582493627654</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.390253119286629</v>
       </c>
       <c r="E52">
-        <v>-30.4451615182128</v>
+        <v>-34.40731362343192</v>
       </c>
       <c r="F52">
-        <v>-1.178132937025016</v>
+        <v>-1.29221044152595</v>
       </c>
       <c r="G52">
-        <v>-15.91802609041689</v>
+        <v>-21.99985081915799</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.691103489340231</v>
       </c>
       <c r="E53">
-        <v>-31.77984092673049</v>
+        <v>-35.53446438936309</v>
       </c>
       <c r="F53">
-        <v>-1.282624269619795</v>
+        <v>-1.446479234748906</v>
       </c>
       <c r="G53">
-        <v>-16.37595233631827</v>
+        <v>-20.51043472576712</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.979257760794644</v>
       </c>
       <c r="E54">
-        <v>-29.80741425947558</v>
+        <v>-34.74903680052473</v>
       </c>
       <c r="F54">
-        <v>-1.418141984803948</v>
+        <v>-1.261319465792346</v>
       </c>
       <c r="G54">
-        <v>-16.51840180032757</v>
+        <v>-19.56352600626046</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.251589377266264</v>
       </c>
       <c r="E55">
-        <v>-29.45240680388127</v>
+        <v>-35.79756646497174</v>
       </c>
       <c r="F55">
-        <v>-1.403887047859078</v>
+        <v>-1.397423152165212</v>
       </c>
       <c r="G55">
-        <v>-16.4508302553255</v>
+        <v>-21.04543543764104</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.501368258710369</v>
       </c>
       <c r="E56">
-        <v>-29.77919507369678</v>
+        <v>-34.29143676628664</v>
       </c>
       <c r="F56">
-        <v>-1.474701666014995</v>
+        <v>-1.518953576704204</v>
       </c>
       <c r="G56">
-        <v>-16.25436427502468</v>
+        <v>-20.33813903844851</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.726575016925185</v>
       </c>
       <c r="E57">
-        <v>-29.57351857697941</v>
+        <v>-34.31548296326738</v>
       </c>
       <c r="F57">
-        <v>-0.9699785500292317</v>
+        <v>-1.185458368736881</v>
       </c>
       <c r="G57">
-        <v>-16.34057915723115</v>
+        <v>-23.05440358214682</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.926186365957869</v>
       </c>
       <c r="E58">
-        <v>-29.53929463466644</v>
+        <v>-32.37168078021495</v>
       </c>
       <c r="F58">
-        <v>-1.389562427853928</v>
+        <v>-1.698861776845168</v>
       </c>
       <c r="G58">
-        <v>-16.52403965938095</v>
+        <v>-21.41270901504055</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.096541834039758</v>
       </c>
       <c r="E59">
-        <v>-27.97638013616217</v>
+        <v>-33.20410940077893</v>
       </c>
       <c r="F59">
-        <v>-1.485869960130674</v>
+        <v>-1.751622939418033</v>
       </c>
       <c r="G59">
-        <v>-17.36696083295356</v>
+        <v>-20.74891483950682</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.23762651427392</v>
       </c>
       <c r="E60">
-        <v>-28.27995091974035</v>
+        <v>-32.54981736225468</v>
       </c>
       <c r="F60">
-        <v>-1.612513379217663</v>
+        <v>-1.22310860131758</v>
       </c>
       <c r="G60">
-        <v>-16.80909418303989</v>
+        <v>-22.51419207159409</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.353571189139209</v>
       </c>
       <c r="E61">
-        <v>-29.33162108091168</v>
+        <v>-30.33705552246469</v>
       </c>
       <c r="F61">
-        <v>-1.650092345032168</v>
+        <v>-1.940175006445465</v>
       </c>
       <c r="G61">
-        <v>-17.37127281851846</v>
+        <v>-22.75634689088239</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.446024343477911</v>
       </c>
       <c r="E62">
-        <v>-27.93542008876279</v>
+        <v>-31.66016694412979</v>
       </c>
       <c r="F62">
-        <v>-1.647539411096479</v>
+        <v>-1.895359296450359</v>
       </c>
       <c r="G62">
-        <v>-17.53039915568183</v>
+        <v>-23.13535800749139</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.516783147941292</v>
       </c>
       <c r="E63">
-        <v>-26.98675912584394</v>
+        <v>-31.15460357743946</v>
       </c>
       <c r="F63">
-        <v>-1.446396882041304</v>
+        <v>-1.372322205258454</v>
       </c>
       <c r="G63">
-        <v>-17.00691417646627</v>
+        <v>-23.01061003048057</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.572269067060957</v>
       </c>
       <c r="E64">
-        <v>-27.34400138336104</v>
+        <v>-30.7413554176325</v>
       </c>
       <c r="F64">
-        <v>-1.935693118704771</v>
+        <v>-1.775843345835806</v>
       </c>
       <c r="G64">
-        <v>-17.35685373742216</v>
+        <v>-24.10441593192854</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.616039497822232</v>
       </c>
       <c r="E65">
-        <v>-26.7564228239178</v>
+        <v>-32.17095390558796</v>
       </c>
       <c r="F65">
-        <v>-1.700116071930196</v>
+        <v>-1.825444223254412</v>
       </c>
       <c r="G65">
-        <v>-17.28112335293856</v>
+        <v>-21.47811877380547</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.648174994533111</v>
       </c>
       <c r="E66">
-        <v>-27.13736711439104</v>
+        <v>-33.64941236384918</v>
       </c>
       <c r="F66">
-        <v>-1.546181440655397</v>
+        <v>-2.27480177228937</v>
       </c>
       <c r="G66">
-        <v>-17.02493844165483</v>
+        <v>-21.62833808819544</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.673219927776207</v>
       </c>
       <c r="E67">
-        <v>-26.98654175909157</v>
+        <v>-30.39224856367018</v>
       </c>
       <c r="F67">
-        <v>-1.701371950721139</v>
+        <v>-1.97253091015085</v>
       </c>
       <c r="G67">
-        <v>-17.72914279131367</v>
+        <v>-23.16880113852911</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.69393458478415</v>
       </c>
       <c r="E68">
-        <v>-27.3054867119258</v>
+        <v>-33.83292198029901</v>
       </c>
       <c r="F68">
-        <v>-2.033281869067108</v>
+        <v>-2.251056477646229</v>
       </c>
       <c r="G68">
-        <v>-16.76387047570068</v>
+        <v>-21.87168635915065</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.706929366225199</v>
       </c>
       <c r="E69">
-        <v>-27.44355082747165</v>
+        <v>-30.28074621241631</v>
       </c>
       <c r="F69">
-        <v>-1.92397686234235</v>
+        <v>-2.134325473883975</v>
       </c>
       <c r="G69">
-        <v>-16.94803115823202</v>
+        <v>-20.40805113914685</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.713169362866265</v>
       </c>
       <c r="E70">
-        <v>-26.82769194785051</v>
+        <v>-32.45750441960832</v>
       </c>
       <c r="F70">
-        <v>-1.796997697601288</v>
+        <v>-1.883587610380898</v>
       </c>
       <c r="G70">
-        <v>-17.11545041197128</v>
+        <v>-21.06609986289716</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.714626027509858</v>
       </c>
       <c r="E71">
-        <v>-26.76584204985375</v>
+        <v>-33.84801311992958</v>
       </c>
       <c r="F71">
-        <v>-2.044082743410405</v>
+        <v>-2.608605802910204</v>
       </c>
       <c r="G71">
-        <v>-17.30269652294523</v>
+        <v>-20.44162007091505</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.705935257999006</v>
       </c>
       <c r="E72">
-        <v>-27.64429355175767</v>
+        <v>-32.14381023238598</v>
       </c>
       <c r="F72">
-        <v>-1.898037343153367</v>
+        <v>-2.700386311827666</v>
       </c>
       <c r="G72">
-        <v>-16.55971244283936</v>
+        <v>-21.78145081938673</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.68569596047999</v>
       </c>
       <c r="E73">
-        <v>-26.98871542661525</v>
+        <v>-31.28910151970427</v>
       </c>
       <c r="F73">
-        <v>-2.457182929217292</v>
+        <v>-2.102124773358303</v>
       </c>
       <c r="G73">
-        <v>-17.20132761853274</v>
+        <v>-20.81984824350402</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.656689616008227</v>
       </c>
       <c r="E74">
-        <v>-27.84283090920196</v>
+        <v>-30.42239008666523</v>
       </c>
       <c r="F74">
-        <v>-2.360513520138868</v>
+        <v>-2.864526344021557</v>
       </c>
       <c r="G74">
-        <v>-16.78449682968311</v>
+        <v>-21.36121016863165</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.613954101342002</v>
       </c>
       <c r="E75">
-        <v>-28.16865461405384</v>
+        <v>-33.13789631807578</v>
       </c>
       <c r="F75">
-        <v>-2.209102524240322</v>
+        <v>-2.52671949669945</v>
       </c>
       <c r="G75">
-        <v>-16.78245422308537</v>
+        <v>-20.99878157462885</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.555793188138169</v>
       </c>
       <c r="E76">
-        <v>-27.44404443113849</v>
+        <v>-30.3151603506376</v>
       </c>
       <c r="F76">
-        <v>-2.247716441870566</v>
+        <v>-2.462276127441345</v>
       </c>
       <c r="G76">
-        <v>-16.14735585628605</v>
+        <v>-21.16975966482282</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.486752537591198</v>
       </c>
       <c r="E77">
-        <v>-28.04102863109567</v>
+        <v>-31.04647946779532</v>
       </c>
       <c r="F77">
-        <v>-2.522410232903538</v>
+        <v>-3.328813488721362</v>
       </c>
       <c r="G77">
-        <v>-16.60145345627126</v>
+        <v>-20.14111026540602</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.406149735428816</v>
       </c>
       <c r="E78">
-        <v>-28.6095921281807</v>
+        <v>-32.09789603442221</v>
       </c>
       <c r="F78">
-        <v>-2.697962449924086</v>
+        <v>-3.085189632190439</v>
       </c>
       <c r="G78">
-        <v>-15.65953869471059</v>
+        <v>-21.14082384153683</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.314747689861506</v>
       </c>
       <c r="E79">
-        <v>-28.34452243061573</v>
+        <v>-35.25768632225129</v>
       </c>
       <c r="F79">
-        <v>-2.670340243199949</v>
+        <v>-3.371377960757671</v>
       </c>
       <c r="G79">
-        <v>-15.56956303277151</v>
+        <v>-18.39265060465825</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.218955852649238</v>
       </c>
       <c r="E80">
-        <v>-28.9064969980196</v>
+        <v>-32.13289208155349</v>
       </c>
       <c r="F80">
-        <v>-2.6427014075637</v>
+        <v>-2.37033328866755</v>
       </c>
       <c r="G80">
-        <v>-15.83330426424863</v>
+        <v>-18.63110919985196</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.119973754672747</v>
       </c>
       <c r="E81">
-        <v>-29.07584834048445</v>
+        <v>-34.19704978254477</v>
       </c>
       <c r="F81">
-        <v>-2.286461015238835</v>
+        <v>-2.909140131512444</v>
       </c>
       <c r="G81">
-        <v>-15.27583653507244</v>
+        <v>-19.33662287027158</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.01677409196792</v>
       </c>
       <c r="E82">
-        <v>-29.8297419005704</v>
+        <v>-32.83147033163575</v>
       </c>
       <c r="F82">
-        <v>-2.874913871120924</v>
+        <v>-2.956436716824085</v>
       </c>
       <c r="G82">
-        <v>-15.38115326504051</v>
+        <v>-18.27259036013104</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.912713494696539</v>
       </c>
       <c r="E83">
-        <v>-29.88302166150765</v>
+        <v>-35.54497044906089</v>
       </c>
       <c r="F83">
-        <v>-2.913116817066112</v>
+        <v>-3.021717074658499</v>
       </c>
       <c r="G83">
-        <v>-15.04510309789463</v>
+        <v>-19.53870188053423</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.807480199557265</v>
       </c>
       <c r="E84">
-        <v>-31.22713614562032</v>
+        <v>-33.94444470968591</v>
       </c>
       <c r="F84">
-        <v>-2.763472445116239</v>
+        <v>-2.840800845702359</v>
       </c>
       <c r="G84">
-        <v>-15.21116668323555</v>
+        <v>-17.12514037876472</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.697126612079995</v>
       </c>
       <c r="E85">
-        <v>-31.7805564256237</v>
+        <v>-36.31393703488137</v>
       </c>
       <c r="F85">
-        <v>-3.018209957908758</v>
+        <v>-3.02415439806236</v>
       </c>
       <c r="G85">
-        <v>-15.44196302077861</v>
+        <v>-17.93458035002591</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.582308654893268</v>
       </c>
       <c r="E86">
-        <v>-31.98521175145235</v>
+        <v>-38.14884753194536</v>
       </c>
       <c r="F86">
-        <v>-2.877590334118017</v>
+        <v>-1.99917992958995</v>
       </c>
       <c r="G86">
-        <v>-15.08494054764145</v>
+        <v>-16.74144318494488</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.463833476269206</v>
       </c>
       <c r="E87">
-        <v>-32.87828569592704</v>
+        <v>-37.64240111282353</v>
       </c>
       <c r="F87">
-        <v>-2.936025914985902</v>
+        <v>-3.675994291356956</v>
       </c>
       <c r="G87">
-        <v>-14.8478475524827</v>
+        <v>-17.31667861203034</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.338701523862722</v>
       </c>
       <c r="E88">
-        <v>-33.50221884470387</v>
+        <v>-36.60913693425638</v>
       </c>
       <c r="F88">
-        <v>-3.005659088528901</v>
+        <v>-3.48593295259211</v>
       </c>
       <c r="G88">
-        <v>-14.61201753044717</v>
+        <v>-16.27583481811963</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.206682169294883</v>
       </c>
       <c r="E89">
-        <v>-35.08847536248068</v>
+        <v>-39.31639907873596</v>
       </c>
       <c r="F89">
-        <v>-3.015730666298138</v>
+        <v>-3.555878116200451</v>
       </c>
       <c r="G89">
-        <v>-14.28497204716811</v>
+        <v>-16.32043779817023</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.069167781450069</v>
       </c>
       <c r="E90">
-        <v>-36.67565116048105</v>
+        <v>-40.37807263899023</v>
       </c>
       <c r="F90">
-        <v>-3.175555891725414</v>
+        <v>-3.065096363388301</v>
       </c>
       <c r="G90">
-        <v>-14.41057414492806</v>
+        <v>-18.2570672120974</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.922999241373905</v>
       </c>
       <c r="E91">
-        <v>-37.42380035128826</v>
+        <v>-40.74559453250474</v>
       </c>
       <c r="F91">
-        <v>-3.017745932075535</v>
+        <v>-3.394886491366454</v>
       </c>
       <c r="G91">
-        <v>-14.17454217961464</v>
+        <v>-16.86054171599293</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.76472219791783</v>
       </c>
       <c r="E92">
-        <v>-38.98867794327487</v>
+        <v>-41.41817707754596</v>
       </c>
       <c r="F92">
-        <v>-3.556668385452255</v>
+        <v>-3.585114119252421</v>
       </c>
       <c r="G92">
-        <v>-14.67587960917249</v>
+        <v>-17.26023050004022</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.593988881583172</v>
       </c>
       <c r="E93">
-        <v>-39.83223755294969</v>
+        <v>-44.26298935577152</v>
       </c>
       <c r="F93">
-        <v>-3.585171132665377</v>
+        <v>-3.615946497867154</v>
       </c>
       <c r="G93">
-        <v>-14.41199933478272</v>
+        <v>-17.70861575369742</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.405895497666443</v>
       </c>
       <c r="E94">
-        <v>-40.53640846843142</v>
+        <v>-43.57917619519128</v>
       </c>
       <c r="F94">
-        <v>-3.569804434167867</v>
+        <v>-4.246887016048652</v>
       </c>
       <c r="G94">
-        <v>-13.97336363773867</v>
+        <v>-17.19861297119054</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.194334333710066</v>
       </c>
       <c r="E95">
-        <v>-42.06050941621595</v>
+        <v>-43.94427761934869</v>
       </c>
       <c r="F95">
-        <v>-3.429355850615993</v>
+        <v>-3.484202753879492</v>
       </c>
       <c r="G95">
-        <v>-14.2123386780365</v>
+        <v>-19.76571095398036</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.957332449810986</v>
       </c>
       <c r="E96">
-        <v>-43.49562811398676</v>
+        <v>-48.22234965676491</v>
       </c>
       <c r="F96">
-        <v>-3.477016688288186</v>
+        <v>-3.982994099358977</v>
       </c>
       <c r="G96">
-        <v>-14.23734488376739</v>
+        <v>-16.06659178730999</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.6945753874568</v>
       </c>
       <c r="E97">
-        <v>-44.3184110849144</v>
+        <v>-48.13374327009383</v>
       </c>
       <c r="F97">
-        <v>-3.625557217214998</v>
+        <v>-4.476203673339496</v>
       </c>
       <c r="G97">
-        <v>-14.13439188331436</v>
+        <v>-16.43761455753273</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.400901156867557</v>
       </c>
       <c r="E98">
-        <v>-46.8494001144084</v>
+        <v>-50.09831756341944</v>
       </c>
       <c r="F98">
-        <v>-3.966352517599539</v>
+        <v>-4.009437237029069</v>
       </c>
       <c r="G98">
-        <v>-14.72741983740063</v>
+        <v>-18.04451529102126</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.087156770217265</v>
       </c>
       <c r="E99">
-        <v>-48.2474917444555</v>
+        <v>-52.62020209592102</v>
       </c>
       <c r="F99">
-        <v>-3.99674462596978</v>
+        <v>-3.503546929783627</v>
       </c>
       <c r="G99">
-        <v>-14.73829829004267</v>
+        <v>-17.61306513307021</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.7515922472241446</v>
       </c>
       <c r="E100">
-        <v>-49.61341988786312</v>
+        <v>-54.12210786047546</v>
       </c>
       <c r="F100">
-        <v>-4.209665175918079</v>
+        <v>-4.056999093081547</v>
       </c>
       <c r="G100">
-        <v>-15.40763266353637</v>
+        <v>-18.71726614751149</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.415746157924148</v>
       </c>
       <c r="E101">
-        <v>-51.94434659629076</v>
+        <v>-54.45959012166009</v>
       </c>
       <c r="F101">
-        <v>-3.890873093669696</v>
+        <v>-4.335299774336932</v>
       </c>
       <c r="G101">
-        <v>-14.69464709183461</v>
+        <v>-17.2104878980399</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.06819090594415522</v>
       </c>
       <c r="E102">
-        <v>-53.23290123280331</v>
+        <v>-53.70170810809189</v>
       </c>
       <c r="F102">
-        <v>-4.259547952989633</v>
+        <v>-4.527420722644807</v>
       </c>
       <c r="G102">
-        <v>-14.85113326893042</v>
+        <v>-17.59298170855622</v>
       </c>
     </row>
   </sheetData>
